--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N125_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N125_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>72.61832952695978</v>
+        <v>11.80047854813096</v>
       </c>
       <c r="D2" t="n">
-        <v>72.35524825352296</v>
+        <v>11.75772784119748</v>
       </c>
       <c r="E2" t="n">
-        <v>17.61206487088638</v>
+        <v>2.861960541519037</v>
       </c>
       <c r="F2" t="n">
-        <v>19.80163207460473</v>
+        <v>3.217765212123268</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.74150628985864</v>
+        <v>4.345494772102029</v>
       </c>
       <c r="D3" t="n">
-        <v>25.91574570791161</v>
+        <v>4.211308677535636</v>
       </c>
       <c r="E3" t="n">
-        <v>17.61206487088638</v>
+        <v>2.861960541519037</v>
       </c>
       <c r="F3" t="n">
-        <v>19.80163207460473</v>
+        <v>3.217765212123268</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.81504213511942</v>
+        <v>2.407444346956905</v>
       </c>
       <c r="D4" t="n">
-        <v>13.99129989000537</v>
+        <v>2.273586232125872</v>
       </c>
       <c r="E4" t="n">
-        <v>17.61206487088638</v>
+        <v>2.861960541519037</v>
       </c>
       <c r="F4" t="n">
-        <v>19.80163207460473</v>
+        <v>3.217765212123268</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.44923879315846</v>
+        <v>2.18550130388825</v>
       </c>
       <c r="D5" t="n">
-        <v>13.95871569559213</v>
+        <v>2.268291300533722</v>
       </c>
       <c r="E5" t="n">
-        <v>17.61206487088638</v>
+        <v>2.861960541519037</v>
       </c>
       <c r="F5" t="n">
-        <v>19.80163207460473</v>
+        <v>3.217765212123268</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.29573601152507</v>
+        <v>6.223057101872825</v>
       </c>
       <c r="D6" t="n">
-        <v>34.76274280879691</v>
+        <v>5.648945706429497</v>
       </c>
       <c r="E6" t="n">
-        <v>17.61206487088638</v>
+        <v>2.861960541519037</v>
       </c>
       <c r="F6" t="n">
-        <v>19.80163207460473</v>
+        <v>3.217765212123268</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.48025874907383</v>
+        <v>6.903042046724498</v>
       </c>
       <c r="D7" t="n">
-        <v>7.165316064609167</v>
+        <v>1.16436386049899</v>
       </c>
       <c r="E7" t="n">
-        <v>17.61206487088638</v>
+        <v>2.861960541519037</v>
       </c>
       <c r="F7" t="n">
-        <v>19.80163207460473</v>
+        <v>3.217765212123268</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.56835512500775</v>
+        <v>6.10485770781376</v>
       </c>
       <c r="D8" t="n">
-        <v>25.87342098840764</v>
+        <v>4.204430910616242</v>
       </c>
       <c r="E8" t="n">
-        <v>17.61206487088638</v>
+        <v>2.861960541519037</v>
       </c>
       <c r="F8" t="n">
-        <v>19.80163207460473</v>
+        <v>3.217765212123268</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>45.20422178255735</v>
+        <v>7.34568603966557</v>
       </c>
       <c r="D9" t="n">
-        <v>30.6758699428825</v>
+        <v>4.984828865718407</v>
       </c>
       <c r="E9" t="n">
-        <v>17.61206487088638</v>
+        <v>2.861960541519037</v>
       </c>
       <c r="F9" t="n">
-        <v>19.80163207460473</v>
+        <v>3.217765212123268</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>61.51206057505708</v>
+        <v>9.995709843446775</v>
       </c>
       <c r="D10" t="n">
-        <v>60.0254971120339</v>
+        <v>9.75414328070551</v>
       </c>
       <c r="E10" t="n">
-        <v>17.61206487088638</v>
+        <v>2.861960541519037</v>
       </c>
       <c r="F10" t="n">
-        <v>19.80163207460473</v>
+        <v>3.217765212123268</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>44.35163441015488</v>
+        <v>7.207140591650168</v>
       </c>
       <c r="D11" t="n">
-        <v>44.87575631417165</v>
+        <v>7.292310401052893</v>
       </c>
       <c r="E11" t="n">
-        <v>17.61206487088638</v>
+        <v>2.861960541519037</v>
       </c>
       <c r="F11" t="n">
-        <v>19.80163207460473</v>
+        <v>3.217765212123268</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
